--- a/Accounts_Scenarios.xlsx
+++ b/Accounts_Scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoj.TRANSITUSNEXGEN.000\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F40288-3B7E-4D0A-B0B3-416F92BAC223}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D3D992-F4B2-42CA-A7A9-3FEC7C9A417F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
   <si>
     <t>TestScenarioID</t>
   </si>
@@ -170,6 +170,15 @@
   </si>
   <si>
     <t>Approved</t>
+  </si>
+  <si>
+    <t>step 4</t>
+  </si>
+  <si>
+    <t>Verify Account is Deleted</t>
+  </si>
+  <si>
+    <t>User should be able to validate the Account is Verified</t>
   </si>
 </sst>
 </file>
@@ -237,8 +246,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:J14" totalsRowShown="0">
-  <autoFilter ref="A1:J14" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
+  <autoFilter ref="A1:J15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TestScenarioID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="TestCaseID"/>
@@ -540,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -802,6 +811,17 @@
         <v>48</v>
       </c>
     </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <tableParts count="1">

--- a/Accounts_Scenarios.xlsx
+++ b/Accounts_Scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoj.TRANSITUSNEXGEN.000\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D3D992-F4B2-42CA-A7A9-3FEC7C9A417F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141315CC-971D-4237-B8F8-C00804E4C95C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
   <si>
     <t>TestScenarioID</t>
   </si>
@@ -170,9 +170,6 @@
   </si>
   <si>
     <t>Approved</t>
-  </si>
-  <si>
-    <t>step 4</t>
   </si>
   <si>
     <t>Verify Account is Deleted</t>
@@ -813,13 +810,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
         <v>50</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>51</v>
-      </c>
-      <c r="H15" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
